--- a/results/12-2025/beta/contributions-12-2025.xlsx
+++ b/results/12-2025/beta/contributions-12-2025.xlsx
@@ -22360,13 +22360,13 @@
         <v>-0.0490826207762288</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.468576240141246</v>
+        <v>-0.66103528812346</v>
       </c>
       <c r="G224" t="n">
         <v>-0.0121592125752994</v>
       </c>
       <c r="H224" t="n">
-        <v>0.186143507905587</v>
+        <v>0.00304391069017393</v>
       </c>
       <c r="I224" t="n">
         <v>0.231077957116543</v>
@@ -22405,7 +22405,7 @@
         <v>-0.00864041923431711</v>
       </c>
       <c r="U224" t="n">
-        <v>-0.0301092869542944</v>
+        <v>0.000136413613387469</v>
       </c>
       <c r="V224" t="n">
         <v>-0.000054499509357388</v>
@@ -22423,19 +22423,19 @@
         <v>-0.279004739493987</v>
       </c>
       <c r="AA224" t="n">
-        <v>-0.0485616432163655</v>
+        <v>-0.424097876092466</v>
       </c>
       <c r="AB224" t="n">
-        <v>0.392798300542418</v>
+        <v>0.422911741577191</v>
       </c>
       <c r="AC224" t="n">
-        <v>0.344433935781732</v>
+        <v>0.000667718277273786</v>
       </c>
       <c r="AD224" t="n">
-        <v>0.334488630730503</v>
+        <v>-0.00927758677395492</v>
       </c>
       <c r="AE224" t="n">
-        <v>-0.0539029669320396</v>
+        <v>-0.139844521308154</v>
       </c>
     </row>
     <row r="225">
@@ -22449,19 +22449,19 @@
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.422988124626581</v>
+        <v>-0.558103826649757</v>
       </c>
       <c r="E225" t="n">
         <v>-0.312542278018482</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.367473670259129</v>
+        <v>-0.551151632014199</v>
       </c>
       <c r="G225" t="n">
         <v>0.0175593413989885</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0663986010456872</v>
+        <v>0.00578474500742265</v>
       </c>
       <c r="I225" t="n">
         <v>0.138341009290489</v>
@@ -22470,7 +22470,7 @@
         <v>0.0195173991436186</v>
       </c>
       <c r="K225" t="n">
-        <v>0.186956618837806</v>
+        <v>0.21060949226688</v>
       </c>
       <c r="L225" t="n">
         <v>0.0259473474648345</v>
@@ -22500,7 +22500,7 @@
         <v>-0.00761687648214987</v>
       </c>
       <c r="U225" t="n">
-        <v>-0.0243087123585196</v>
+        <v>0.00007166641002684</v>
       </c>
       <c r="V225" t="n">
         <v>-0.00051123717965773</v>
@@ -22512,25 +22512,25 @@
         <v>0.0485143726340999</v>
       </c>
       <c r="Y225" t="n">
-        <v>-0.546052738063675</v>
+        <v>-0.681168440086851</v>
       </c>
       <c r="Z225" t="n">
         <v>-0.189477664581388</v>
       </c>
       <c r="AA225" t="n">
-        <v>-0.124895209053012</v>
+        <v>-0.368957007818326</v>
       </c>
       <c r="AB225" t="n">
-        <v>0.449568658128264</v>
+        <v>0.497406560272943</v>
       </c>
       <c r="AC225" t="n">
-        <v>-0.574728997672437</v>
+        <v>-0.769598033142075</v>
       </c>
       <c r="AD225" t="n">
-        <v>-1.3102594003175</v>
+        <v>-1.64024413781031</v>
       </c>
       <c r="AE225" t="n">
-        <v>-0.517876020148152</v>
+        <v>-0.68631375889747</v>
       </c>
     </row>
     <row r="226">
@@ -22544,19 +22544,19 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0.845133726475321</v>
+        <v>0.631453565072001</v>
       </c>
       <c r="E226" t="n">
         <v>-0.249048765220945</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.122429005901385</v>
+        <v>-0.625318287598449</v>
       </c>
       <c r="G226" t="n">
         <v>0.00590255020553988</v>
       </c>
       <c r="H226" t="n">
-        <v>0.063452241899417</v>
+        <v>0.00447246411443217</v>
       </c>
       <c r="I226" t="n">
         <v>0.310452477049513</v>
@@ -22565,7 +22565,7 @@
         <v>0.0159246971580387</v>
       </c>
       <c r="K226" t="n">
-        <v>0.126493109834028</v>
+        <v>0.149603996222549</v>
       </c>
       <c r="L226" t="n">
         <v>0.0401761764622805</v>
@@ -22595,37 +22595,37 @@
         <v>-0.00697925811468748</v>
       </c>
       <c r="U226" t="n">
-        <v>-0.0225747008991583</v>
+        <v>-0.000177578608138042</v>
       </c>
       <c r="V226" t="n">
         <v>-0.0004332982847647</v>
       </c>
       <c r="W226" t="n">
-        <v>0.329395740370807</v>
+        <v>0.329307100591226</v>
       </c>
       <c r="X226" t="n">
-        <v>0.0589447646826733</v>
+        <v>0.0589013947381581</v>
       </c>
       <c r="Y226" t="n">
-        <v>0.783288560771929</v>
+        <v>0.56960839936861</v>
       </c>
       <c r="Z226" t="n">
         <v>-0.187203599517553</v>
       </c>
       <c r="AA226" t="n">
-        <v>0.273521476195746</v>
+        <v>-0.28640897744384</v>
       </c>
       <c r="AB226" t="n">
-        <v>0.49828528059925</v>
+        <v>0.543439607988362</v>
       </c>
       <c r="AC226" t="n">
-        <v>2.43034970783787</v>
+        <v>1.91869306982339</v>
       </c>
       <c r="AD226" t="n">
-        <v>3.02643466909225</v>
+        <v>2.30109786967445</v>
       </c>
       <c r="AE226" t="n">
-        <v>0.403979849112183</v>
+        <v>0.0542079105084155</v>
       </c>
     </row>
     <row r="227">
@@ -22639,19 +22639,19 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>0.0251600512038947</v>
+        <v>-0.100583283051727</v>
       </c>
       <c r="E227" t="n">
         <v>-0.197351648298297</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.0831008314572705</v>
+        <v>-0.578984997049026</v>
       </c>
       <c r="G227" t="n">
         <v>0.00025649148136205</v>
       </c>
       <c r="H227" t="n">
-        <v>0.0605991292704738</v>
+        <v>0.00299999560841865</v>
       </c>
       <c r="I227" t="n">
         <v>0.246395558170962</v>
@@ -22660,7 +22660,7 @@
         <v>0.0134983266082235</v>
       </c>
       <c r="K227" t="n">
-        <v>-0.0666414818372443</v>
+        <v>-0.0439070771286188</v>
       </c>
       <c r="L227" t="n">
         <v>0.0494532352939022</v>
@@ -22690,37 +22690,37 @@
         <v>-0.00640203419761886</v>
       </c>
       <c r="U227" t="n">
-        <v>-0.0207710092403272</v>
+        <v>-0.00019779480954661</v>
       </c>
       <c r="V227" t="n">
         <v>-0.000403155345719388</v>
       </c>
       <c r="W227" t="n">
-        <v>0.249093301129796</v>
+        <v>0.248916831983053</v>
       </c>
       <c r="X227" t="n">
-        <v>0.0627576447439376</v>
+        <v>0.0626717148094236</v>
       </c>
       <c r="Y227" t="n">
-        <v>-0.0593708987935443</v>
+        <v>-0.185114233049166</v>
       </c>
       <c r="Z227" t="n">
         <v>-0.112820698300857</v>
       </c>
       <c r="AA227" t="n">
-        <v>0.237728467849977</v>
+        <v>-0.314255655265487</v>
       </c>
       <c r="AB227" t="n">
-        <v>0.249118763076234</v>
+        <v>0.292023557880945</v>
       </c>
       <c r="AC227" t="n">
-        <v>0.046215173227408</v>
+        <v>-0.461253559089122</v>
       </c>
       <c r="AD227" t="n">
-        <v>-0.125976423866994</v>
+        <v>-0.759188490439145</v>
       </c>
       <c r="AE227" t="n">
-        <v>0.481171868909564</v>
+        <v>-0.0269030863372406</v>
       </c>
     </row>
     <row r="228">
@@ -22734,19 +22734,19 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.0390608485606986</v>
+        <v>-0.109807929514999</v>
       </c>
       <c r="E228" t="n">
         <v>-0.187165166029055</v>
       </c>
       <c r="F228" t="n">
-        <v>-0.138646323235453</v>
+        <v>-0.422412416439981</v>
       </c>
       <c r="G228" t="n">
         <v>0.0130422731557438</v>
       </c>
       <c r="H228" t="n">
-        <v>0.0656395868798085</v>
+        <v>0.0098103842164881</v>
       </c>
       <c r="I228" t="n">
         <v>0.0758032222607924</v>
@@ -22755,7 +22755,7 @@
         <v>0.0125707709789203</v>
       </c>
       <c r="K228" t="n">
-        <v>0.12525670259847</v>
+        <v>0.147398946401835</v>
       </c>
       <c r="L228" t="n">
         <v>0.0562452208187217</v>
@@ -22785,37 +22785,37 @@
         <v>-0.00570967373767366</v>
       </c>
       <c r="U228" t="n">
-        <v>-0.018828308383142</v>
+        <v>-0.00719841848913463</v>
       </c>
       <c r="V228" t="n">
         <v>-0.000373542104317482</v>
       </c>
       <c r="W228" t="n">
-        <v>0.174589445415704</v>
+        <v>0.174328200632589</v>
       </c>
       <c r="X228" t="n">
-        <v>0.00303413065082872</v>
+        <v>0.00290618188041283</v>
       </c>
       <c r="Y228" t="n">
-        <v>-0.0737117766014559</v>
+        <v>-0.144458857555756</v>
       </c>
       <c r="Z228" t="n">
         <v>-0.152514237988298</v>
       </c>
       <c r="AA228" t="n">
-        <v>0.028563766903677</v>
+        <v>-0.310715735346977</v>
       </c>
       <c r="AB228" t="n">
-        <v>0.318031400809007</v>
+        <v>0.351324682621119</v>
       </c>
       <c r="AC228" t="n">
-        <v>0.306497717601708</v>
+        <v>0.00177934134246731</v>
       </c>
       <c r="AD228" t="n">
-        <v>0.080271703011954</v>
+        <v>-0.295193754201586</v>
       </c>
       <c r="AE228" t="n">
-        <v>0.417617636979927</v>
+        <v>-0.0983821281941484</v>
       </c>
     </row>
     <row r="229">
@@ -22829,19 +22829,19 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.133889800297776</v>
+        <v>-0.128768276802932</v>
       </c>
       <c r="E229" t="n">
         <v>-0.19794770947525</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.116627035364636</v>
+        <v>-0.396779681868301</v>
       </c>
       <c r="G229" t="n">
         <v>0.0242316440709545</v>
       </c>
       <c r="H229" t="n">
-        <v>0.07163659685413</v>
+        <v>0.0171723190733515</v>
       </c>
       <c r="I229" t="n">
         <v>-0.0526970445352275</v>
@@ -22850,7 +22850,7 @@
         <v>0.0141414410572426</v>
       </c>
       <c r="K229" t="n">
-        <v>0.123887640533058</v>
+        <v>0.146197157814443</v>
       </c>
       <c r="L229" t="n">
         <v>0.00938938626835879</v>
@@ -22880,37 +22880,37 @@
         <v>-0.00317381549787083</v>
       </c>
       <c r="U229" t="n">
-        <v>-0.0119078230323711</v>
+        <v>-0.0060832323506638</v>
       </c>
       <c r="V229" t="n">
         <v>-0.00032736315334269</v>
       </c>
       <c r="W229" t="n">
-        <v>0.11642825866365</v>
+        <v>0.151513877124217</v>
       </c>
       <c r="X229" t="n">
-        <v>-0.00527018367242113</v>
+        <v>0.0118600272695753</v>
       </c>
       <c r="Y229" t="n">
-        <v>-0.193124106720723</v>
+        <v>-0.18800258322588</v>
       </c>
       <c r="Z229" t="n">
         <v>-0.138713403052302</v>
       </c>
       <c r="AA229" t="n">
-        <v>-0.0592139678364409</v>
+        <v>-0.393898571857753</v>
       </c>
       <c r="AB229" t="n">
-        <v>0.222638601299626</v>
+        <v>0.302845094260753</v>
       </c>
       <c r="AC229" t="n">
-        <v>0.123565660541756</v>
+        <v>-0.129777958711042</v>
       </c>
       <c r="AD229" t="n">
-        <v>-0.208271849231269</v>
+        <v>-0.456493944989224</v>
       </c>
       <c r="AE229" t="n">
-        <v>0.693114524751485</v>
+        <v>0.197555420011124</v>
       </c>
     </row>
     <row r="230">
@@ -22924,19 +22924,19 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.0632676098402536</v>
+        <v>-0.0551857869712319</v>
       </c>
       <c r="E230" t="n">
         <v>-0.202166726760656</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.315316565878134</v>
+        <v>-0.630853686925339</v>
       </c>
       <c r="G230" t="n">
         <v>0.0155798021279945</v>
       </c>
       <c r="H230" t="n">
-        <v>0.0789942017510026</v>
+        <v>0.03001080269654</v>
       </c>
       <c r="I230" t="n">
         <v>-0.265919569872781</v>
@@ -22945,7 +22945,7 @@
         <v>0.0140451689752763</v>
       </c>
       <c r="K230" t="n">
-        <v>0.117499575997341</v>
+        <v>0.139421692604589</v>
       </c>
       <c r="L230" t="n">
         <v>0.0102963915436851</v>
@@ -22975,37 +22975,37 @@
         <v>-0.00179353053893329</v>
       </c>
       <c r="U230" t="n">
-        <v>-0.011377663947453</v>
+        <v>-0.00563738618981608</v>
       </c>
       <c r="V230" t="n">
         <v>-0.000320869501234469</v>
       </c>
       <c r="W230" t="n">
-        <v>0.107804840529417</v>
+        <v>0.142864586083492</v>
       </c>
       <c r="X230" t="n">
-        <v>-0.00247849398233307</v>
+        <v>0.0146371213735088</v>
       </c>
       <c r="Y230" t="n">
-        <v>-0.108565195116675</v>
+        <v>-0.100483372247653</v>
       </c>
       <c r="Z230" t="n">
         <v>-0.156869141484235</v>
       </c>
       <c r="AA230" t="n">
-        <v>-0.472864266508273</v>
+        <v>-0.838366540423123</v>
       </c>
       <c r="AB230" t="n">
-        <v>0.219616679468501</v>
+        <v>0.2993106195484</v>
       </c>
       <c r="AC230" t="n">
-        <v>-0.192139176914293</v>
+        <v>-0.476378995616372</v>
       </c>
       <c r="AD230" t="n">
-        <v>-0.457573513515203</v>
+        <v>-0.733731509348261</v>
       </c>
       <c r="AE230" t="n">
-        <v>-0.177887520900378</v>
+        <v>-0.561151924744554</v>
       </c>
     </row>
     <row r="231">
@@ -23019,19 +23019,19 @@
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.109994932615649</v>
+        <v>-0.102588326655568</v>
       </c>
       <c r="E231" t="n">
         <v>-0.190669553816339</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.163980623383405</v>
+        <v>-0.473352712165434</v>
       </c>
       <c r="G231" t="n">
         <v>0.0212990634605951</v>
       </c>
       <c r="H231" t="n">
-        <v>0.0876465872138879</v>
+        <v>0.0401370113452621</v>
       </c>
       <c r="I231" t="n">
         <v>-0.361639787806169</v>
@@ -23040,7 +23040,7 @@
         <v>0.0129199797540298</v>
       </c>
       <c r="K231" t="n">
-        <v>0.122120596078609</v>
+        <v>0.143534590874196</v>
       </c>
       <c r="L231" t="n">
         <v>0.0105096931760416</v>
@@ -23070,37 +23070,37 @@
         <v>-0.00150839009602481</v>
       </c>
       <c r="U231" t="n">
-        <v>-0.0094192493134395</v>
+        <v>-0.00518510375621118</v>
       </c>
       <c r="V231" t="n">
         <v>-0.000313583602102981</v>
       </c>
       <c r="W231" t="n">
-        <v>0.0899031322437616</v>
+        <v>0.124779357859762</v>
       </c>
       <c r="X231" t="n">
-        <v>0.00225265532257926</v>
+        <v>0.0192716113707925</v>
       </c>
       <c r="Y231" t="n">
-        <v>-0.154348893060319</v>
+        <v>-0.146942287100238</v>
       </c>
       <c r="Z231" t="n">
         <v>-0.146315593371669</v>
       </c>
       <c r="AA231" t="n">
-        <v>-0.403738190755085</v>
+        <v>-0.761821084717515</v>
       </c>
       <c r="AB231" t="n">
-        <v>0.215054166182543</v>
+        <v>0.292458544440502</v>
       </c>
       <c r="AC231" t="n">
-        <v>-0.127753107565849</v>
+        <v>-0.406974922313196</v>
       </c>
       <c r="AD231" t="n">
-        <v>-0.428417593997837</v>
+        <v>-0.700232802785103</v>
       </c>
       <c r="AE231" t="n">
-        <v>-0.253497813433088</v>
+        <v>-0.546413002831043</v>
       </c>
     </row>
     <row r="232">
@@ -23114,19 +23114,19 @@
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.107327237075905</v>
+        <v>-0.0998781369166413</v>
       </c>
       <c r="E232" t="n">
         <v>-0.185945349193385</v>
       </c>
       <c r="F232" t="n">
-        <v>0.0430080134692555</v>
+        <v>-0.156506486249321</v>
       </c>
       <c r="G232" t="n">
         <v>0.0299149386979397</v>
       </c>
       <c r="H232" t="n">
-        <v>0.0849421096961252</v>
+        <v>0.0387084747650609</v>
       </c>
       <c r="I232" t="n">
         <v>-0.383632959495008</v>
@@ -23135,7 +23135,7 @@
         <v>0.0127924392151031</v>
       </c>
       <c r="K232" t="n">
-        <v>0.121790796605558</v>
+        <v>0.142780107595241</v>
       </c>
       <c r="L232" t="n">
         <v>0.0107140588144347</v>
@@ -23165,37 +23165,37 @@
         <v>-0.00124682906474473</v>
       </c>
       <c r="U232" t="n">
-        <v>0.0253478857120107</v>
+        <v>-0.00308668026813357</v>
       </c>
       <c r="V232" t="n">
         <v>-0.000307559702302357</v>
       </c>
       <c r="W232" t="n">
-        <v>0.0777413643131754</v>
+        <v>0.112545740961953</v>
       </c>
       <c r="X232" t="n">
-        <v>0.000986896413409566</v>
+        <v>0.0179828340477685</v>
       </c>
       <c r="Y232" t="n">
-        <v>-0.150654993135316</v>
+        <v>-0.143205892976052</v>
       </c>
       <c r="Z232" t="n">
         <v>-0.142617593133974</v>
       </c>
       <c r="AA232" t="n">
-        <v>-0.212375254107607</v>
+        <v>-0.458917256751006</v>
       </c>
       <c r="AB232" t="n">
-        <v>0.238059596836302</v>
+        <v>0.282354294581283</v>
       </c>
       <c r="AC232" t="n">
-        <v>0.0262271634394462</v>
+        <v>-0.175172243185305</v>
       </c>
       <c r="AD232" t="n">
-        <v>-0.267045422829844</v>
+        <v>-0.460995729295331</v>
       </c>
       <c r="AE232" t="n">
-        <v>-0.340327094893538</v>
+        <v>-0.587863496604479</v>
       </c>
     </row>
     <row r="233">
@@ -23209,19 +23209,19 @@
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>-6.60557352979572</v>
+        <v>-6.47806975312735</v>
       </c>
       <c r="E233" t="n">
         <v>-10.9037578876447</v>
       </c>
       <c r="F233" t="n">
-        <v>7.83077878329621</v>
+        <v>8.21297803869525</v>
       </c>
       <c r="G233" t="n">
         <v>3.95183122591064</v>
       </c>
       <c r="H233" t="n">
-        <v>0.225003638380444</v>
+        <v>0.231272574320292</v>
       </c>
       <c r="I233" t="n">
         <v>-1.04223723144777</v>
@@ -23230,7 +23230,7 @@
         <v>0.0795326465091398</v>
       </c>
       <c r="K233" t="n">
-        <v>-7.59919414287477</v>
+        <v>-7.64918221474259</v>
       </c>
       <c r="L233" t="n">
         <v>-0.681918222798813</v>
@@ -23260,37 +23260,37 @@
         <v>-0.000242564189780229</v>
       </c>
       <c r="U233" t="n">
-        <v>0.0221809145286732</v>
+        <v>-0.00171261840578641</v>
       </c>
       <c r="V233" t="n">
         <v>-0.000244291494816687</v>
       </c>
       <c r="W233" t="n">
-        <v>-6.24314226372513</v>
+        <v>-6.28076109005346</v>
       </c>
       <c r="X233" t="n">
-        <v>-1.04145947439162</v>
+        <v>-1.0588517924932</v>
       </c>
       <c r="Y233" t="n">
-        <v>-8.22198236289931</v>
+        <v>-8.09447858623094</v>
       </c>
       <c r="Z233" t="n">
         <v>-9.28734905454106</v>
       </c>
       <c r="AA233" t="n">
-        <v>10.8010271406709</v>
+        <v>11.1749391175104</v>
       </c>
       <c r="AB233" t="n">
-        <v>-16.4996250979217</v>
+        <v>-16.6434537281169</v>
       </c>
       <c r="AC233" t="n">
-        <v>-3.79844730842385</v>
+        <v>-3.48428963602994</v>
       </c>
       <c r="AD233" t="n">
-        <v>-21.3077787258642</v>
+        <v>-20.8661172768019</v>
       </c>
       <c r="AE233" t="n">
-        <v>-5.61520381405178</v>
+        <v>-5.69026932955766</v>
       </c>
     </row>
     <row r="234">
@@ -23310,13 +23310,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F234" t="n">
-        <v>7.67379851846076</v>
+        <v>8.22619163786476</v>
       </c>
       <c r="G234" t="n">
         <v>3.91471096462309</v>
       </c>
       <c r="H234" t="n">
-        <v>0.205019911370051</v>
+        <v>0.211204235371887</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -23325,7 +23325,7 @@
         <v>0.0822314974286476</v>
       </c>
       <c r="K234" t="n">
-        <v>-7.65771128572966</v>
+        <v>-7.70681027751427</v>
       </c>
       <c r="L234" t="n">
         <v>-0.678822568938048</v>
@@ -23355,16 +23355,16 @@
         <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>0.0204399136848129</v>
+        <v>-0.00168122366672296</v>
       </c>
       <c r="V234" t="n">
         <v>-0.000239841382250929</v>
       </c>
       <c r="W234" t="n">
-        <v>-6.21783688023931</v>
+        <v>-6.25529835540234</v>
       </c>
       <c r="X234" t="n">
-        <v>-1.03739651392816</v>
+        <v>-1.05472052348822</v>
       </c>
       <c r="Y234" t="e">
         <v>#NUM!</v>
@@ -23373,19 +23373,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA234" t="n">
-        <v>11.5114154984536</v>
+        <v>12.0434488368993</v>
       </c>
       <c r="AB234" t="n">
-        <v>-16.4997153506638</v>
+        <v>-16.640215517986</v>
       </c>
       <c r="AC234" t="n">
-        <v>-2.96179308750823</v>
+        <v>-2.45654476383655</v>
       </c>
       <c r="AD234" t="n">
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>-5.50081043567297</v>
+        <v>-5.50683645222059</v>
       </c>
     </row>
     <row r="235">
@@ -23405,13 +23405,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F235" t="n">
-        <v>3.84797462170817</v>
+        <v>4.1286983820478</v>
       </c>
       <c r="G235" t="n">
         <v>1.96364581398549</v>
       </c>
       <c r="H235" t="n">
-        <v>0.201236820287628</v>
+        <v>0.207347837192536</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -23420,7 +23420,7 @@
         <v>0.0800842219637856</v>
       </c>
       <c r="K235" t="n">
-        <v>-7.58910231621931</v>
+        <v>-7.63720006107641</v>
       </c>
       <c r="L235" t="n">
         <v>-0.674784520518673</v>
@@ -23450,16 +23450,16 @@
         <v>0</v>
       </c>
       <c r="U235" t="n">
-        <v>0.0190398683822629</v>
+        <v>-0.00132089125871762</v>
       </c>
       <c r="V235" t="n">
         <v>-0.000235115116044392</v>
       </c>
       <c r="W235" t="n">
-        <v>-6.18410697780855</v>
+        <v>-6.22136221215495</v>
       </c>
       <c r="X235" t="n">
-        <v>-1.03178194856953</v>
+        <v>-1.04901177451744</v>
       </c>
       <c r="Y235" t="e">
         <v>#NUM!</v>
@@ -23468,19 +23468,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA235" t="n">
-        <v>5.9934031881908</v>
+        <v>6.2729673778217</v>
       </c>
       <c r="AB235" t="n">
-        <v>-16.3706573690992</v>
+        <v>-16.5075777856877</v>
       </c>
       <c r="AC235" t="n">
-        <v>-9.34108189849621</v>
+        <v>-9.14064530224005</v>
       </c>
       <c r="AD235" t="n">
         <v>0</v>
       </c>
       <c r="AE235" t="n">
-        <v>-5.39370603717352</v>
+        <v>-5.33177825152432</v>
       </c>
     </row>
     <row r="236">
@@ -23500,13 +23500,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F236" t="n">
-        <v>3.81031457523063</v>
+        <v>4.08752868128894</v>
       </c>
       <c r="G236" t="n">
         <v>1.94516894228386</v>
       </c>
       <c r="H236" t="n">
-        <v>0.0424130801398416</v>
+        <v>0.207356425689043</v>
       </c>
       <c r="I236" t="n">
         <v>0</v>
@@ -23515,7 +23515,7 @@
         <v>0.0722050383116069</v>
       </c>
       <c r="K236" t="n">
-        <v>-7.53667931610028</v>
+        <v>-7.58388822222526</v>
       </c>
       <c r="L236" t="n">
         <v>-0.672192275821125</v>
@@ -23545,16 +23545,16 @@
         <v>0</v>
       </c>
       <c r="U236" t="n">
-        <v>0.0121224500248692</v>
+        <v>0</v>
       </c>
       <c r="V236" t="n">
         <v>-0.000230930912567213</v>
       </c>
       <c r="W236" t="n">
-        <v>-6.16291112293303</v>
+        <v>-6.20002793844189</v>
       </c>
       <c r="X236" t="n">
-        <v>-1.02901738936579</v>
+        <v>-1.046200656882</v>
       </c>
       <c r="Y236" t="e">
         <v>#NUM!</v>
@@ -23563,19 +23563,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA236" t="n">
-        <v>5.78282506412055</v>
+        <v>6.20801614199932</v>
       </c>
       <c r="AB236" t="n">
-        <v>-16.2815032610648</v>
+        <v>-16.4075156508281</v>
       </c>
       <c r="AC236" t="n">
-        <v>-9.50607599062192</v>
+        <v>-9.12495585440191</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>-5.32694468146605</v>
+        <v>-5.21652931920049</v>
       </c>
     </row>
     <row r="237">
@@ -23595,13 +23595,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F237" t="n">
-        <v>3.76889757576956</v>
+        <v>4.04233433839637</v>
       </c>
       <c r="G237" t="n">
         <v>1.92593712683849</v>
       </c>
       <c r="H237" t="n">
-        <v>0.141894843675121</v>
+        <v>0.202329960214326</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
@@ -23640,7 +23640,7 @@
         <v>0</v>
       </c>
       <c r="U237" t="n">
-        <v>0.00668988589557848</v>
+        <v>0</v>
       </c>
       <c r="V237" t="n">
         <v>-0.0000775425198130453</v>
@@ -23658,19 +23658,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA237" t="n">
-        <v>5.81392160384073</v>
+        <v>6.13754616869073</v>
       </c>
       <c r="AB237" t="n">
-        <v>-0.0858350415587553</v>
+        <v>-0.0925315530974514</v>
       </c>
       <c r="AC237" t="n">
-        <v>5.73348537387624</v>
+        <v>6.05116229253296</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -23690,13 +23690,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F238" t="n">
-        <v>3.84259183020517</v>
+        <v>4.1289735590324</v>
       </c>
       <c r="G238" t="n">
         <v>1.90911045121583</v>
       </c>
       <c r="H238" t="n">
-        <v>0.138540681878872</v>
+        <v>0.197547029419631</v>
       </c>
       <c r="I238" t="n">
         <v>0</v>
@@ -23735,7 +23735,7 @@
         <v>0</v>
       </c>
       <c r="U238" t="n">
-        <v>0.00656793941301944</v>
+        <v>0</v>
       </c>
       <c r="V238" t="n">
         <v>-0.0000761335626973866</v>
@@ -23753,19 +23753,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA238" t="n">
-        <v>5.86571399878314</v>
+        <v>6.20068128691994</v>
       </c>
       <c r="AB238" t="n">
-        <v>-0.0679615010009962</v>
+        <v>-0.0745346730703333</v>
       </c>
       <c r="AC238" t="n">
-        <v>5.8020597389782</v>
+        <v>6.13114332624384</v>
       </c>
       <c r="AD238" t="n">
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -23785,13 +23785,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F239" t="n">
-        <v>3.7939986856712</v>
+        <v>4.07653198957659</v>
       </c>
       <c r="G239" t="n">
         <v>1.88983262508393</v>
       </c>
       <c r="H239" t="n">
-        <v>0.135170547120995</v>
+        <v>0.192741261514678</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
@@ -23830,7 +23830,7 @@
         <v>0</v>
       </c>
       <c r="U239" t="n">
-        <v>0.00516552929660426</v>
+        <v>0</v>
       </c>
       <c r="V239" t="n">
         <v>-0.0000747012046274973</v>
@@ -23848,19 +23848,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA239" t="n">
-        <v>5.79564542637517</v>
+        <v>6.12563811932823</v>
       </c>
       <c r="AB239" t="n">
-        <v>-0.06973715678133</v>
+        <v>-0.0749068184202304</v>
       </c>
       <c r="AC239" t="n">
-        <v>5.73027086623317</v>
+        <v>6.05568716568284</v>
       </c>
       <c r="AD239" t="n">
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -23880,13 +23880,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F240" t="n">
-        <v>3.74214620936576</v>
+        <v>4.02058793660349</v>
       </c>
       <c r="G240" t="n">
         <v>1.86888125857121</v>
       </c>
       <c r="H240" t="n">
-        <v>0.131720256759676</v>
+        <v>0.187821507750366</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
@@ -23943,19 +23943,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA240" t="n">
-        <v>5.72034354854001</v>
+        <v>6.04508415184639</v>
       </c>
       <c r="AB240" t="n">
         <v>-0.06976854096555</v>
       </c>
       <c r="AC240" t="n">
-        <v>5.6548840665987</v>
+        <v>5.97987209538218</v>
       </c>
       <c r="AD240" t="n">
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -23981,7 +23981,7 @@
         <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>0.128458217362767</v>
+        <v>0.183169966378849</v>
       </c>
       <c r="I241" t="n">
         <v>0</v>
@@ -24038,19 +24038,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA241" t="n">
-        <v>0.192140141576493</v>
+        <v>0.246814597889677</v>
       </c>
       <c r="AB241" t="n">
         <v>-0.041420773178431</v>
       </c>
       <c r="AC241" t="n">
-        <v>0.150804402492</v>
+        <v>0.205503066347682</v>
       </c>
       <c r="AD241" t="n">
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -24076,7 +24076,7 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>0.129126565893671</v>
+        <v>0.178758143195854</v>
       </c>
       <c r="I242" t="n">
         <v>0</v>
@@ -24133,19 +24133,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA242" t="n">
-        <v>0.19153250650442</v>
+        <v>0.24113097668148</v>
       </c>
       <c r="AB242" t="n">
         <v>-0.0403569472672376</v>
       </c>
       <c r="AC242" t="n">
-        <v>0.151258035719205</v>
+        <v>0.200877872844728</v>
       </c>
       <c r="AD242" t="n">
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -24171,7 +24171,7 @@
         <v>0</v>
       </c>
       <c r="H243" t="n">
-        <v>0.126077420306515</v>
+        <v>0.174538215695995</v>
       </c>
       <c r="I243" t="n">
         <v>0</v>
@@ -24228,19 +24228,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA243" t="n">
-        <v>0.187161424119097</v>
+        <v>0.235590653609687</v>
       </c>
       <c r="AB243" t="n">
         <v>-0.0395516580667302</v>
       </c>
       <c r="AC243" t="n">
-        <v>0.147688567251145</v>
+        <v>0.196138195602093</v>
       </c>
       <c r="AD243" t="n">
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -24266,7 +24266,7 @@
         <v>0</v>
       </c>
       <c r="H244" t="n">
-        <v>0.122836462527538</v>
+        <v>0.170052651685828</v>
       </c>
       <c r="I244" t="n">
         <v>0</v>
@@ -24323,19 +24323,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA244" t="n">
-        <v>0.182460376475291</v>
+        <v>0.22964654812383</v>
       </c>
       <c r="AB244" t="n">
         <v>-0.0387730626082901</v>
       </c>
       <c r="AC244" t="n">
-        <v>0.143762620403908</v>
+        <v>0.190968275065099</v>
       </c>
       <c r="AD244" t="n">
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -24430,7 +24430,7 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -24525,7 +24525,7 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -24620,7 +24620,7 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -24715,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -24810,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -24905,7 +24905,7 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -25000,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -25095,7 +25095,7 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -25190,7 +25190,7 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -25285,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -25380,7 +25380,7 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="AE256" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -25570,7 +25570,7 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -25760,7 +25760,7 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -25855,7 +25855,7 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
